--- a/tapdrill/tapdrill.xlsx
+++ b/tapdrill/tapdrill.xlsx
@@ -219,24 +219,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -249,15 +245,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -450,14 +437,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="7.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8.47"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="16" style="1" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="16" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="12.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="20" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16382" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -520,66 +510,62 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="I2" s="3" t="n">
+      <c r="A2" s="3"/>
+      <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="I3" s="3" t="n">
+      <c r="A3" s="3"/>
+      <c r="I3" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.85</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="I4" s="3" t="n">
+      <c r="A4" s="3"/>
+      <c r="I4" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.95</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="I5" s="3" t="n">
+      <c r="A5" s="3"/>
+      <c r="I5" s="1" t="n">
         <v>1.4</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -630,18 +616,17 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="I8" s="3" t="n">
+      <c r="A8" s="3"/>
+      <c r="I8" s="1" t="n">
         <v>1.7</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -690,8 +675,8 @@
       <c r="O10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="0"/>
-      <c r="Q10" s="0"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
       <c r="R10" s="1" t="n">
         <v>2.1</v>
       </c>
@@ -721,8 +706,8 @@
       <c r="O11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I12" s="1" t="n">
@@ -746,8 +731,8 @@
       <c r="O12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
       <c r="R12" s="1" t="n">
         <v>2.3</v>
       </c>
@@ -866,34 +851,32 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="I17" s="3" t="n">
+      <c r="A17" s="3"/>
+      <c r="I17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J17" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="1" t="n">
         <v>3.6</v>
       </c>
-      <c r="L17" s="3"/>
-      <c r="O17" s="3" t="s">
+      <c r="O17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="I18" s="3" t="n">
+      <c r="A18" s="3"/>
+      <c r="I18" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J18" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="L18" s="3"/>
-      <c r="O18" s="3" t="s">
+      <c r="O18" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -973,18 +956,17 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="I22" s="3" t="n">
+      <c r="A22" s="3"/>
+      <c r="I22" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="L22" s="3"/>
-      <c r="O22" s="3" t="s">
+      <c r="O22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1081,18 +1063,17 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="I27" s="3" t="n">
+      <c r="A27" s="3"/>
+      <c r="I27" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="J27" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="1" t="n">
         <v>5.5</v>
       </c>
-      <c r="L27" s="3"/>
-      <c r="O27" s="3" t="s">
+      <c r="O27" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1201,34 +1182,32 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="I32" s="3" t="n">
+      <c r="A32" s="3"/>
+      <c r="I32" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="J32" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="1" t="n">
         <v>7.5</v>
       </c>
-      <c r="L32" s="3"/>
-      <c r="O32" s="3" t="s">
+      <c r="O32" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="I33" s="3" t="n">
+      <c r="A33" s="3"/>
+      <c r="I33" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="J33" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="1" t="n">
         <v>7.25</v>
       </c>
-      <c r="L33" s="3"/>
-      <c r="O33" s="3" t="s">
+      <c r="O33" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1337,18 +1316,17 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="I38" s="3" t="n">
+      <c r="A38" s="3"/>
+      <c r="I38" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="J38" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="1" t="n">
         <v>9.25</v>
       </c>
-      <c r="L38" s="3"/>
-      <c r="O38" s="3" t="s">
+      <c r="O38" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1440,18 +1418,17 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="I42" s="3" t="n">
+      <c r="A42" s="3"/>
+      <c r="I42" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="J42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="L42" s="3"/>
-      <c r="O42" s="3" t="s">
+      <c r="O42" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1479,34 +1456,32 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-      <c r="I44" s="3" t="n">
+      <c r="A44" s="3"/>
+      <c r="I44" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="J44" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="1" t="n">
         <v>11.25</v>
       </c>
-      <c r="L44" s="3"/>
-      <c r="O44" s="3" t="s">
+      <c r="O44" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="I45" s="3" t="n">
+      <c r="A45" s="3"/>
+      <c r="I45" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="J45" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="L45" s="3"/>
-      <c r="O45" s="3" t="s">
+      <c r="O45" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1595,18 +1570,17 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="I49" s="3" t="n">
+      <c r="A49" s="3"/>
+      <c r="I49" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="J49" s="3" t="n">
+      <c r="J49" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="L49" s="3"/>
-      <c r="O49" s="3" t="s">
+      <c r="O49" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1712,18 +1686,17 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="I54" s="3" t="n">
+      <c r="A54" s="3"/>
+      <c r="I54" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="J54" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="L54" s="3"/>
-      <c r="O54" s="3" t="s">
+      <c r="O54" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1806,18 +1779,17 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="I58" s="3" t="n">
+      <c r="A58" s="3"/>
+      <c r="I58" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="J58" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="L58" s="3"/>
-      <c r="O58" s="3" t="s">
+      <c r="O58" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1926,18 +1898,17 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="I63" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J63" s="3" t="n">
+      <c r="A63" s="3"/>
+      <c r="I63" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J63" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K63" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L63" s="3"/>
-      <c r="O63" s="3" t="s">
+      <c r="K63" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="O63" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2020,34 +1991,32 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="I67" s="3" t="n">
+      <c r="A67" s="3"/>
+      <c r="I67" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="J67" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K67" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="L67" s="3"/>
-      <c r="O67" s="3" t="s">
+      <c r="O67" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="I68" s="3" t="n">
+      <c r="A68" s="3"/>
+      <c r="I68" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="J68" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="L68" s="3"/>
-      <c r="O68" s="3" t="s">
+      <c r="O68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R68" s="1" t="n">
@@ -2058,18 +2027,17 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="I69" s="3" t="n">
+      <c r="A69" s="3"/>
+      <c r="I69" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="J69" s="3" t="n">
+      <c r="J69" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K69" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L69" s="3"/>
-      <c r="O69" s="3" t="s">
+      <c r="K69" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O69" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R69" s="1" t="n">
@@ -2080,18 +2048,17 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="I70" s="3" t="n">
+      <c r="A70" s="3"/>
+      <c r="I70" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="J70" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" s="1" t="n">
         <v>19.5</v>
       </c>
-      <c r="L70" s="3"/>
-      <c r="O70" s="3" t="s">
+      <c r="O70" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R70" s="1" t="n">
@@ -2102,34 +2069,32 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="I71" s="3" t="n">
+      <c r="A71" s="3"/>
+      <c r="I71" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="J71" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="1" t="n">
         <v>22.5</v>
       </c>
-      <c r="L71" s="3"/>
-      <c r="O71" s="3" t="s">
+      <c r="O71" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="I72" s="3" t="n">
+      <c r="A72" s="3"/>
+      <c r="I72" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="J72" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="L72" s="3"/>
-      <c r="O72" s="3" t="s">
+      <c r="O72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R72" s="1" t="n">
@@ -2140,18 +2105,17 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="I73" s="3" t="n">
+      <c r="A73" s="3"/>
+      <c r="I73" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="J73" s="3" t="n">
+      <c r="J73" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="L73" s="3"/>
-      <c r="O73" s="3" t="s">
+      <c r="O73" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R73" s="1" t="n">
@@ -2162,50 +2126,47 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="I74" s="3" t="n">
+      <c r="A74" s="3"/>
+      <c r="I74" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="J74" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="K74" s="1" t="n">
         <v>24.5</v>
       </c>
-      <c r="L74" s="3"/>
-      <c r="O74" s="3" t="s">
+      <c r="O74" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="I75" s="3" t="n">
+      <c r="A75" s="3"/>
+      <c r="I75" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="J75" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="K75" s="1" t="n">
         <v>25.5</v>
       </c>
-      <c r="L75" s="3"/>
-      <c r="O75" s="3" t="s">
+      <c r="O75" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="I76" s="3" t="n">
+      <c r="A76" s="3"/>
+      <c r="I76" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="J76" s="3" t="n">
+      <c r="J76" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="K76" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="L76" s="3"/>
-      <c r="O76" s="3" t="s">
+      <c r="O76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R76" s="1" t="n">
@@ -2216,18 +2177,17 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="I77" s="3" t="n">
+      <c r="A77" s="3"/>
+      <c r="I77" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="J77" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K77" s="3" t="n">
+      <c r="K77" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="L77" s="3"/>
-      <c r="O77" s="3" t="s">
+      <c r="O77" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R77" s="1" t="n">
@@ -2238,50 +2198,47 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="I78" s="3" t="n">
+      <c r="A78" s="3"/>
+      <c r="I78" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="J78" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="K78" s="1" t="n">
         <v>26.5</v>
       </c>
-      <c r="L78" s="3"/>
-      <c r="O78" s="3" t="s">
+      <c r="O78" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="I79" s="3" t="n">
+      <c r="A79" s="3"/>
+      <c r="I79" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="J79" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="K79" s="1" t="n">
         <v>28.5</v>
       </c>
-      <c r="L79" s="3"/>
-      <c r="O79" s="3" t="s">
+      <c r="O79" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="I80" s="3" t="n">
+      <c r="A80" s="3"/>
+      <c r="I80" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="J80" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="K80" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="L80" s="3"/>
-      <c r="O80" s="3" t="s">
+      <c r="O80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R80" s="1" t="n">
@@ -2292,18 +2249,17 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="I81" s="3" t="n">
+      <c r="A81" s="3"/>
+      <c r="I81" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="J81" s="3" t="n">
+      <c r="J81" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="K81" s="1" t="n">
         <v>26.5</v>
       </c>
-      <c r="L81" s="3"/>
-      <c r="O81" s="3" t="s">
+      <c r="O81" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R81" s="1" t="n">
@@ -2314,18 +2270,17 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="I82" s="3" t="n">
+      <c r="A82" s="3"/>
+      <c r="I82" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="J82" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="L82" s="3"/>
-      <c r="O82" s="3" t="s">
+      <c r="O82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R82" s="1" t="n">
@@ -2336,18 +2291,17 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-      <c r="I83" s="3" t="n">
+      <c r="A83" s="3"/>
+      <c r="I83" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="J83" s="3" t="n">
+      <c r="J83" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="K83" s="1" t="n">
         <v>29.5</v>
       </c>
-      <c r="L83" s="3"/>
-      <c r="O83" s="3" t="s">
+      <c r="O83" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R83" s="1" t="n">
@@ -2358,16 +2312,14 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-      <c r="I84" s="3" t="n">
+      <c r="A84" s="3"/>
+      <c r="I84" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="J84" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="O84" s="3" t="s">
+      <c r="O84" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R84" s="1" t="n">
@@ -2378,18 +2330,17 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-      <c r="I85" s="3" t="n">
+      <c r="A85" s="3"/>
+      <c r="I85" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="J85" s="3" t="n">
+      <c r="J85" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="K85" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="L85" s="3"/>
-      <c r="O85" s="3" t="s">
+      <c r="O85" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R85" s="1" t="n">
@@ -2400,18 +2351,17 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-      <c r="I86" s="3" t="n">
+      <c r="A86" s="3"/>
+      <c r="I86" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="J86" s="3" t="n">
+      <c r="J86" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="K86" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="L86" s="3"/>
-      <c r="O86" s="3" t="s">
+      <c r="O86" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R86" s="1" t="n">
@@ -2422,16 +2372,14 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
-      <c r="I87" s="3" t="n">
+      <c r="A87" s="3"/>
+      <c r="I87" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="J87" s="3" t="n">
+      <c r="J87" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="O87" s="3" t="s">
+      <c r="O87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R87" s="1" t="n">
@@ -2442,18 +2390,17 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="I88" s="3" t="n">
+      <c r="A88" s="3"/>
+      <c r="I88" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="J88" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="K88" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="L88" s="3"/>
-      <c r="O88" s="3" t="s">
+      <c r="O88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R88" s="1" t="n">
@@ -2464,18 +2411,17 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-      <c r="I89" s="3" t="n">
+      <c r="A89" s="3"/>
+      <c r="I89" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="J89" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="K89" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="L89" s="3"/>
-      <c r="O89" s="3" t="s">
+      <c r="O89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R89" s="1" t="n">
@@ -2614,7 +2560,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B94" s="1" t="n">
@@ -3156,7 +3102,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B110" s="1" t="n">
@@ -3191,7 +3137,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B111" s="1" t="n">
@@ -3226,7 +3172,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B112" s="1" t="n">
@@ -3255,7 +3201,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B113" s="1" t="n">
@@ -3290,7 +3236,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B114" s="1" t="n">
@@ -3325,7 +3271,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B115" s="1" t="n">
@@ -3354,7 +3300,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B116" s="1" t="n">
@@ -3389,7 +3335,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B117" s="1" t="n">
@@ -3424,7 +3370,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B118" s="1" t="n">
@@ -3453,7 +3399,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B119" s="1" t="n">
@@ -3488,7 +3434,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B120" s="1" t="n">
@@ -3523,7 +3469,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B121" s="1" t="n">
@@ -3552,7 +3498,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B122" s="1" t="n">
@@ -3587,7 +3533,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B123" s="1" t="n">
@@ -3622,7 +3568,7 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B124" s="1" t="n">
@@ -3651,7 +3597,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B125" s="1" t="n">
@@ -3686,7 +3632,7 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B126" s="1" t="n">
@@ -3721,7 +3667,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B127" s="1" t="n">
@@ -3750,7 +3696,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B128" s="1" t="n">
@@ -3785,7 +3731,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B129" s="1" t="n">
@@ -3820,7 +3766,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B130" s="1" t="n">
@@ -3849,7 +3795,7 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B131" s="1" t="n">
@@ -3878,7 +3824,7 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B132" s="1" t="n">
@@ -3913,7 +3859,7 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B133" s="1" t="n">
@@ -3948,7 +3894,7 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B134" s="1" t="n">
@@ -3977,7 +3923,7 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B135" s="1" t="n">
@@ -4006,7 +3952,7 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B136" s="1" t="n">
@@ -4041,7 +3987,7 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B137" s="1" t="n">
@@ -4076,7 +4022,7 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B138" s="1" t="n">
@@ -4105,7 +4051,7 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B139" s="1" t="n">
@@ -4134,7 +4080,7 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B140" s="1" t="n">
@@ -4169,7 +4115,7 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B141" s="1" t="n">
@@ -4204,7 +4150,7 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B142" s="1" t="n">
@@ -4227,7 +4173,7 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B143" s="1" t="n">
@@ -4256,7 +4202,7 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B144" s="1" t="n">
@@ -4288,7 +4234,7 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B145" s="1" t="n">
@@ -4320,7 +4266,7 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B146" s="1" t="n">
@@ -4352,7 +4298,7 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B147" s="1" t="n">
@@ -4384,7 +4330,7 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B148" s="1" t="n">
@@ -4416,7 +4362,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B149" s="1" t="n">
@@ -4448,7 +4394,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="2" t="s">
+      <c r="A150" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B150" s="1" t="n">
@@ -4480,7 +4426,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="2" t="s">
+      <c r="A151" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B151" s="1" t="n">
